--- a/data/nzd0028/nzd0028.xlsx
+++ b/data/nzd0028/nzd0028.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN249"/>
+  <dimension ref="A1:AN250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31823,6 +31823,132 @@
         </is>
       </c>
     </row>
+    <row r="250">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>388.44</v>
+      </c>
+      <c r="C250" t="n">
+        <v>404.06</v>
+      </c>
+      <c r="D250" t="n">
+        <v>401.19</v>
+      </c>
+      <c r="E250" t="n">
+        <v>413.79</v>
+      </c>
+      <c r="F250" t="n">
+        <v>413.61</v>
+      </c>
+      <c r="G250" t="n">
+        <v>414.3</v>
+      </c>
+      <c r="H250" t="n">
+        <v>420.36</v>
+      </c>
+      <c r="I250" t="n">
+        <v>418.53</v>
+      </c>
+      <c r="J250" t="n">
+        <v>420.5</v>
+      </c>
+      <c r="K250" t="n">
+        <v>420.24</v>
+      </c>
+      <c r="L250" t="n">
+        <v>421.26</v>
+      </c>
+      <c r="M250" t="n">
+        <v>422.44</v>
+      </c>
+      <c r="N250" t="n">
+        <v>415.2</v>
+      </c>
+      <c r="O250" t="n">
+        <v>412.65</v>
+      </c>
+      <c r="P250" t="n">
+        <v>410.12</v>
+      </c>
+      <c r="Q250" t="n">
+        <v>404.41</v>
+      </c>
+      <c r="R250" t="n">
+        <v>410.92</v>
+      </c>
+      <c r="S250" t="n">
+        <v>407.44</v>
+      </c>
+      <c r="T250" t="n">
+        <v>409.21</v>
+      </c>
+      <c r="U250" t="n">
+        <v>415.54</v>
+      </c>
+      <c r="V250" t="n">
+        <v>415.17</v>
+      </c>
+      <c r="W250" t="n">
+        <v>417.18</v>
+      </c>
+      <c r="X250" t="n">
+        <v>418.69</v>
+      </c>
+      <c r="Y250" t="n">
+        <v>420.83</v>
+      </c>
+      <c r="Z250" t="n">
+        <v>419.93</v>
+      </c>
+      <c r="AA250" t="n">
+        <v>415.09</v>
+      </c>
+      <c r="AB250" t="n">
+        <v>414.46</v>
+      </c>
+      <c r="AC250" t="n">
+        <v>411.47</v>
+      </c>
+      <c r="AD250" t="n">
+        <v>409.24</v>
+      </c>
+      <c r="AE250" t="n">
+        <v>414.28</v>
+      </c>
+      <c r="AF250" t="n">
+        <v>416.58</v>
+      </c>
+      <c r="AG250" t="n">
+        <v>417.47</v>
+      </c>
+      <c r="AH250" t="n">
+        <v>423.72</v>
+      </c>
+      <c r="AI250" t="n">
+        <v>426.32</v>
+      </c>
+      <c r="AJ250" t="n">
+        <v>420.01</v>
+      </c>
+      <c r="AK250" t="n">
+        <v>410.87</v>
+      </c>
+      <c r="AL250" t="n">
+        <v>406.28</v>
+      </c>
+      <c r="AM250" t="n">
+        <v>414.61</v>
+      </c>
+      <c r="AN250" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -31834,7 +31960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B260"/>
+  <dimension ref="A1:B261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34437,6 +34563,16 @@
       </c>
       <c r="B260" t="n">
         <v>-0.24</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>-0.92</v>
       </c>
     </row>
   </sheetData>
@@ -34605,28 +34741,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.005563376424605991</v>
+        <v>-0.005772436446099644</v>
       </c>
       <c r="J2" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K2" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L2" t="n">
-        <v>2.327076071828582e-05</v>
+        <v>2.52942816407753e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>7.530131862442905</v>
+        <v>7.500872574888533</v>
       </c>
       <c r="N2" t="n">
-        <v>85.69603626661674</v>
+        <v>85.35216880362213</v>
       </c>
       <c r="O2" t="n">
-        <v>9.257215362441167</v>
+        <v>9.238623750517288</v>
       </c>
       <c r="P2" t="n">
-        <v>388.8585088218242</v>
+        <v>388.8604201637602</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34683,28 +34819,28 @@
         <v>0.0723</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1629805994103774</v>
+        <v>0.1640961989431198</v>
       </c>
       <c r="J3" t="n">
+        <v>249</v>
+      </c>
+      <c r="K3" t="n">
         <v>248</v>
       </c>
-      <c r="K3" t="n">
-        <v>247</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.02060385011330512</v>
+        <v>0.02107585107712973</v>
       </c>
       <c r="M3" t="n">
-        <v>7.378393746158682</v>
+        <v>7.35400235452914</v>
       </c>
       <c r="N3" t="n">
-        <v>81.52098526023929</v>
+        <v>81.20065512356231</v>
       </c>
       <c r="O3" t="n">
-        <v>9.028897233895139</v>
+        <v>9.0111406116852</v>
       </c>
       <c r="P3" t="n">
-        <v>398.2460126182132</v>
+        <v>398.2358100887408</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34761,28 +34897,28 @@
         <v>0.0752</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1452964636611364</v>
+        <v>0.1436014169101584</v>
       </c>
       <c r="J4" t="n">
+        <v>249</v>
+      </c>
+      <c r="K4" t="n">
         <v>248</v>
       </c>
-      <c r="K4" t="n">
-        <v>247</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.01562620914529422</v>
+        <v>0.01541073943325955</v>
       </c>
       <c r="M4" t="n">
-        <v>7.284384712467892</v>
+        <v>7.26292670472116</v>
       </c>
       <c r="N4" t="n">
-        <v>85.86260997414897</v>
+        <v>85.53574386396315</v>
       </c>
       <c r="O4" t="n">
-        <v>9.266207960873151</v>
+        <v>9.248553609292815</v>
       </c>
       <c r="P4" t="n">
-        <v>399.5094389307187</v>
+        <v>399.524940698088</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34839,28 +34975,28 @@
         <v>0.0809</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1316320092057406</v>
+        <v>0.1306493428770111</v>
       </c>
       <c r="J5" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K5" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01249920879899891</v>
+        <v>0.01243209024470449</v>
       </c>
       <c r="M5" t="n">
-        <v>7.773133984957741</v>
+        <v>7.746034723051546</v>
       </c>
       <c r="N5" t="n">
-        <v>88.202821952045</v>
+        <v>87.85507441656125</v>
       </c>
       <c r="O5" t="n">
-        <v>9.391635744216499</v>
+        <v>9.373103777114668</v>
       </c>
       <c r="P5" t="n">
-        <v>411.5458364662857</v>
+        <v>411.5548205434409</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34917,28 +35053,28 @@
         <v>0.07530000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1391588443210942</v>
+        <v>0.1402552377781541</v>
       </c>
       <c r="J6" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K6" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01335532772218151</v>
+        <v>0.01369170588987256</v>
       </c>
       <c r="M6" t="n">
-        <v>7.64005770952101</v>
+        <v>7.615322320495959</v>
       </c>
       <c r="N6" t="n">
-        <v>92.17908281598629</v>
+        <v>91.81695322089132</v>
       </c>
       <c r="O6" t="n">
-        <v>9.600993845221769</v>
+        <v>9.582116322654997</v>
       </c>
       <c r="P6" t="n">
-        <v>408.4608617765896</v>
+        <v>408.4508379433487</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34995,28 +35131,28 @@
         <v>0.0759</v>
       </c>
       <c r="I7" t="n">
-        <v>0.09047794582975534</v>
+        <v>0.09227993652890953</v>
       </c>
       <c r="J7" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K7" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L7" t="n">
-        <v>0.006664633299829248</v>
+        <v>0.00699540052370673</v>
       </c>
       <c r="M7" t="n">
-        <v>7.347963274359282</v>
+        <v>7.329959441796709</v>
       </c>
       <c r="N7" t="n">
-        <v>78.61576300582345</v>
+        <v>78.3218298242644</v>
       </c>
       <c r="O7" t="n">
-        <v>8.866553050978911</v>
+        <v>8.849962136883095</v>
       </c>
       <c r="P7" t="n">
-        <v>409.5329413413714</v>
+        <v>409.5164665492668</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35073,28 +35209,28 @@
         <v>0.0924</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.03040624038275646</v>
+        <v>-0.03003405138540243</v>
       </c>
       <c r="J8" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K8" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0009540002444560214</v>
+        <v>0.000939773672180233</v>
       </c>
       <c r="M8" t="n">
-        <v>6.474270838631458</v>
+        <v>6.450540128935589</v>
       </c>
       <c r="N8" t="n">
-        <v>62.38310377049774</v>
+        <v>62.13349889935016</v>
       </c>
       <c r="O8" t="n">
-        <v>7.89829752354884</v>
+        <v>7.882480504216306</v>
       </c>
       <c r="P8" t="n">
-        <v>420.6894043705917</v>
+        <v>420.686001613653</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35151,28 +35287,28 @@
         <v>0.09080000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.06039797571081878</v>
+        <v>-0.06230238088965331</v>
       </c>
       <c r="J9" t="n">
+        <v>249</v>
+      </c>
+      <c r="K9" t="n">
         <v>248</v>
       </c>
-      <c r="K9" t="n">
-        <v>247</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.003855976870871913</v>
+        <v>0.004139671692290459</v>
       </c>
       <c r="M9" t="n">
-        <v>6.347130171975981</v>
+        <v>6.329731527296498</v>
       </c>
       <c r="N9" t="n">
-        <v>60.84432359636041</v>
+        <v>60.62341384426077</v>
       </c>
       <c r="O9" t="n">
-        <v>7.800277148689039</v>
+        <v>7.786103893749478</v>
       </c>
       <c r="P9" t="n">
-        <v>422.6223442564669</v>
+        <v>422.6397606764225</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35229,28 +35365,28 @@
         <v>0.0839</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0564665930482416</v>
+        <v>-0.0565238300784406</v>
       </c>
       <c r="J10" t="n">
+        <v>249</v>
+      </c>
+      <c r="K10" t="n">
         <v>248</v>
       </c>
-      <c r="K10" t="n">
-        <v>247</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.003460637071569406</v>
+        <v>0.003500934894702157</v>
       </c>
       <c r="M10" t="n">
-        <v>6.343791005445033</v>
+        <v>6.318451292924821</v>
       </c>
       <c r="N10" t="n">
-        <v>59.28013173450269</v>
+        <v>59.04112101328282</v>
       </c>
       <c r="O10" t="n">
-        <v>7.699359176873274</v>
+        <v>7.683822031598781</v>
       </c>
       <c r="P10" t="n">
-        <v>422.0808261458861</v>
+        <v>422.0813495976</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35307,28 +35443,28 @@
         <v>0.067</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.08087400040511558</v>
+        <v>-0.07939327934963269</v>
       </c>
       <c r="J11" t="n">
+        <v>249</v>
+      </c>
+      <c r="K11" t="n">
         <v>248</v>
       </c>
-      <c r="K11" t="n">
-        <v>247</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.005963159509905003</v>
+        <v>0.005801906599079976</v>
       </c>
       <c r="M11" t="n">
-        <v>6.890248876110682</v>
+        <v>6.871989476295089</v>
       </c>
       <c r="N11" t="n">
-        <v>70.39332726643603</v>
+        <v>70.12425236938799</v>
       </c>
       <c r="O11" t="n">
-        <v>8.390073138324603</v>
+        <v>8.374022472467338</v>
       </c>
       <c r="P11" t="n">
-        <v>420.4801896636797</v>
+        <v>420.4666479762143</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35385,28 +35521,28 @@
         <v>0.0711</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1318339193597219</v>
+        <v>-0.1293368550226633</v>
       </c>
       <c r="J12" t="n">
+        <v>249</v>
+      </c>
+      <c r="K12" t="n">
         <v>248</v>
       </c>
-      <c r="K12" t="n">
-        <v>247</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.01511189207999519</v>
+        <v>0.01468295792601004</v>
       </c>
       <c r="M12" t="n">
-        <v>7.084851808213186</v>
+        <v>7.071796780059763</v>
       </c>
       <c r="N12" t="n">
-        <v>73.13242345764903</v>
+        <v>72.87953654871203</v>
       </c>
       <c r="O12" t="n">
-        <v>8.551749730765572</v>
+        <v>8.536951244367748</v>
       </c>
       <c r="P12" t="n">
-        <v>421.539035438825</v>
+        <v>421.5161989533788</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35463,28 +35599,28 @@
         <v>0.0689</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.08052290052742399</v>
+        <v>-0.07821580221869924</v>
       </c>
       <c r="J13" t="n">
+        <v>249</v>
+      </c>
+      <c r="K13" t="n">
         <v>248</v>
       </c>
-      <c r="K13" t="n">
-        <v>247</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.006895008899673649</v>
+        <v>0.006566517992770637</v>
       </c>
       <c r="M13" t="n">
-        <v>6.223015213478357</v>
+        <v>6.212413546413702</v>
       </c>
       <c r="N13" t="n">
-        <v>60.2957556034198</v>
+        <v>60.08848188781305</v>
       </c>
       <c r="O13" t="n">
-        <v>7.76503416627511</v>
+        <v>7.751676069587341</v>
       </c>
       <c r="P13" t="n">
-        <v>421.592894640961</v>
+        <v>421.5717954581452</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35541,28 +35677,28 @@
         <v>0.0677</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.09247974493400997</v>
+        <v>-0.09362191995906378</v>
       </c>
       <c r="J14" t="n">
+        <v>249</v>
+      </c>
+      <c r="K14" t="n">
         <v>248</v>
       </c>
-      <c r="K14" t="n">
-        <v>247</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.01079641151091115</v>
+        <v>0.01116527110363263</v>
       </c>
       <c r="M14" t="n">
-        <v>5.882586229188475</v>
+        <v>5.863990339689569</v>
       </c>
       <c r="N14" t="n">
-        <v>50.5926103964779</v>
+        <v>50.39739562550839</v>
       </c>
       <c r="O14" t="n">
-        <v>7.112848261876384</v>
+        <v>7.099112312501359</v>
       </c>
       <c r="P14" t="n">
-        <v>419.1640995967305</v>
+        <v>419.1745451679358</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35619,28 +35755,28 @@
         <v>0.07099999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1478145164515924</v>
+        <v>-0.1475446895447934</v>
       </c>
       <c r="J15" t="n">
+        <v>249</v>
+      </c>
+      <c r="K15" t="n">
         <v>248</v>
       </c>
-      <c r="K15" t="n">
-        <v>247</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.02859282299077648</v>
+        <v>0.02875791907862602</v>
       </c>
       <c r="M15" t="n">
-        <v>5.500552522515797</v>
+        <v>5.479971306990676</v>
       </c>
       <c r="N15" t="n">
-        <v>47.92543175042167</v>
+        <v>47.73267447503126</v>
       </c>
       <c r="O15" t="n">
-        <v>6.922819638732593</v>
+        <v>6.908883735816609</v>
       </c>
       <c r="P15" t="n">
-        <v>416.2576528858376</v>
+        <v>416.2551852288618</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35697,28 +35833,28 @@
         <v>0.0746</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1438990922551372</v>
+        <v>-0.1440122467063881</v>
       </c>
       <c r="J16" t="n">
+        <v>249</v>
+      </c>
+      <c r="K16" t="n">
         <v>248</v>
       </c>
-      <c r="K16" t="n">
-        <v>247</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.02908763141148552</v>
+        <v>0.02940452683659789</v>
       </c>
       <c r="M16" t="n">
-        <v>5.420593706492299</v>
+        <v>5.399286628754988</v>
       </c>
       <c r="N16" t="n">
-        <v>44.6247064096993</v>
+        <v>44.44485432613229</v>
       </c>
       <c r="O16" t="n">
-        <v>6.680172633225829</v>
+        <v>6.666697407722379</v>
       </c>
       <c r="P16" t="n">
-        <v>414.1137446103015</v>
+        <v>414.1147794454641</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -35775,28 +35911,28 @@
         <v>0.07140000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.189260268996486</v>
+        <v>-0.1957217031646571</v>
       </c>
       <c r="J17" t="n">
+        <v>249</v>
+      </c>
+      <c r="K17" t="n">
         <v>248</v>
       </c>
-      <c r="K17" t="n">
-        <v>247</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.0457744563237652</v>
+        <v>0.04897265203579482</v>
       </c>
       <c r="M17" t="n">
-        <v>5.555332869262342</v>
+        <v>5.561683494249216</v>
       </c>
       <c r="N17" t="n">
-        <v>48.20968981239928</v>
+        <v>48.29652954439214</v>
       </c>
       <c r="O17" t="n">
-        <v>6.94331979764718</v>
+        <v>6.949570457545714</v>
       </c>
       <c r="P17" t="n">
-        <v>417.8791170743133</v>
+        <v>417.9382090428915</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -35853,28 +35989,28 @@
         <v>0.055</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2171022981037814</v>
+        <v>-0.2163503061363684</v>
       </c>
       <c r="J18" t="n">
+        <v>249</v>
+      </c>
+      <c r="K18" t="n">
         <v>248</v>
       </c>
-      <c r="K18" t="n">
-        <v>247</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.04142165042801982</v>
+        <v>0.04152493055485762</v>
       </c>
       <c r="M18" t="n">
-        <v>6.705795235480499</v>
+        <v>6.683139495057401</v>
       </c>
       <c r="N18" t="n">
-        <v>70.42334439199142</v>
+        <v>70.143188511631</v>
       </c>
       <c r="O18" t="n">
-        <v>8.3918617953343</v>
+        <v>8.37515304407215</v>
       </c>
       <c r="P18" t="n">
-        <v>415.7496955812261</v>
+        <v>415.7428183641018</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -35931,28 +36067,28 @@
         <v>0.0479</v>
       </c>
       <c r="I19" t="n">
-        <v>0.121551204271217</v>
+        <v>0.1188015369028559</v>
       </c>
       <c r="J19" t="n">
+        <v>249</v>
+      </c>
+      <c r="K19" t="n">
         <v>248</v>
       </c>
-      <c r="K19" t="n">
-        <v>247</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.007258881491499558</v>
+        <v>0.007000096075696516</v>
       </c>
       <c r="M19" t="n">
-        <v>9.031287613577266</v>
+        <v>9.007103817762729</v>
       </c>
       <c r="N19" t="n">
-        <v>130.4585130133108</v>
+        <v>129.9834001609391</v>
       </c>
       <c r="O19" t="n">
-        <v>11.42184367837832</v>
+        <v>11.4010262766533</v>
       </c>
       <c r="P19" t="n">
-        <v>407.7699062107075</v>
+        <v>407.7950528350485</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -36009,28 +36145,28 @@
         <v>0.055</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.013041439929704</v>
+        <v>-0.016049580852017</v>
       </c>
       <c r="J20" t="n">
+        <v>249</v>
+      </c>
+      <c r="K20" t="n">
         <v>248</v>
       </c>
-      <c r="K20" t="n">
-        <v>247</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.0001483853934565182</v>
+        <v>0.0002267066059208345</v>
       </c>
       <c r="M20" t="n">
-        <v>7.035046831987623</v>
+        <v>7.021633527566513</v>
       </c>
       <c r="N20" t="n">
-        <v>74.06370281838718</v>
+        <v>73.82575059251333</v>
       </c>
       <c r="O20" t="n">
-        <v>8.606027121639066</v>
+        <v>8.592191256746636</v>
       </c>
       <c r="P20" t="n">
-        <v>413.4653243496138</v>
+        <v>413.492750731205</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -36087,28 +36223,28 @@
         <v>0.0839</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.08118065305507106</v>
+        <v>-0.0800824032198475</v>
       </c>
       <c r="J21" t="n">
+        <v>249</v>
+      </c>
+      <c r="K21" t="n">
         <v>248</v>
       </c>
-      <c r="K21" t="n">
-        <v>247</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.009606269783923982</v>
+        <v>0.009438059558601997</v>
       </c>
       <c r="M21" t="n">
-        <v>5.440355157485502</v>
+        <v>5.424675427026567</v>
       </c>
       <c r="N21" t="n">
-        <v>43.90297499103803</v>
+        <v>43.7340779538081</v>
       </c>
       <c r="O21" t="n">
-        <v>6.625932009237495</v>
+        <v>6.613174574575217</v>
       </c>
       <c r="P21" t="n">
-        <v>416.2805677027292</v>
+        <v>416.2705317043338</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -36165,28 +36301,28 @@
         <v>0.0838</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.065816345039661</v>
+        <v>-0.06695985383465197</v>
       </c>
       <c r="J22" t="n">
+        <v>249</v>
+      </c>
+      <c r="K22" t="n">
         <v>248</v>
       </c>
-      <c r="K22" t="n">
-        <v>247</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.009683748588516616</v>
+        <v>0.01011226787723651</v>
       </c>
       <c r="M22" t="n">
-        <v>4.22462765669458</v>
+        <v>4.212991463699512</v>
       </c>
       <c r="N22" t="n">
-        <v>28.62422179528171</v>
+        <v>28.51761660812256</v>
       </c>
       <c r="O22" t="n">
-        <v>5.350160913026982</v>
+        <v>5.340188817647046</v>
       </c>
       <c r="P22" t="n">
-        <v>418.4202608088277</v>
+        <v>418.4307103914851</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -36243,28 +36379,28 @@
         <v>0.1942</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.09887340253735762</v>
+        <v>-0.09915262808570795</v>
       </c>
       <c r="J23" t="n">
+        <v>249</v>
+      </c>
+      <c r="K23" t="n">
         <v>248</v>
       </c>
-      <c r="K23" t="n">
-        <v>247</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.0222043885025085</v>
+        <v>0.02253710318864344</v>
       </c>
       <c r="M23" t="n">
-        <v>4.075803556443216</v>
+        <v>4.060625195107332</v>
       </c>
       <c r="N23" t="n">
-        <v>27.81659656631996</v>
+        <v>27.70495847206373</v>
       </c>
       <c r="O23" t="n">
-        <v>5.27414415486721</v>
+        <v>5.263549987609477</v>
       </c>
       <c r="P23" t="n">
-        <v>420.1873776826933</v>
+        <v>420.1899292944171</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -36321,28 +36457,28 @@
         <v>0.0851</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1099073637858001</v>
+        <v>-0.1086887091961866</v>
       </c>
       <c r="J24" t="n">
+        <v>249</v>
+      </c>
+      <c r="K24" t="n">
         <v>248</v>
       </c>
-      <c r="K24" t="n">
-        <v>247</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.02138383529073717</v>
+        <v>0.02111370082188679</v>
       </c>
       <c r="M24" t="n">
-        <v>4.857836623709773</v>
+        <v>4.84543502917417</v>
       </c>
       <c r="N24" t="n">
-        <v>35.72038511993578</v>
+        <v>35.58636300396359</v>
       </c>
       <c r="O24" t="n">
-        <v>5.976653337774894</v>
+        <v>5.965430663746214</v>
       </c>
       <c r="P24" t="n">
-        <v>420.0401963711362</v>
+        <v>420.0290600931111</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -36399,28 +36535,28 @@
         <v>0.2</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.09464009767040604</v>
+        <v>-0.09198653852902924</v>
       </c>
       <c r="J25" t="n">
+        <v>249</v>
+      </c>
+      <c r="K25" t="n">
         <v>248</v>
       </c>
-      <c r="K25" t="n">
-        <v>247</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.01864353003479513</v>
+        <v>0.01777049089825633</v>
       </c>
       <c r="M25" t="n">
-        <v>4.330038350544759</v>
+        <v>4.326484679975648</v>
       </c>
       <c r="N25" t="n">
-        <v>30.46384863624782</v>
+        <v>30.38847886073356</v>
       </c>
       <c r="O25" t="n">
-        <v>5.519406547469377</v>
+        <v>5.512574612713514</v>
       </c>
       <c r="P25" t="n">
-        <v>419.9085411324056</v>
+        <v>419.8842924465137</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -36477,28 +36613,28 @@
         <v>0.2</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.08740621817698666</v>
+        <v>-0.08642680033138926</v>
       </c>
       <c r="J26" t="n">
+        <v>249</v>
+      </c>
+      <c r="K26" t="n">
         <v>248</v>
       </c>
-      <c r="K26" t="n">
-        <v>247</v>
-      </c>
       <c r="L26" t="n">
-        <v>0.01881388124768191</v>
+        <v>0.01857180210985765</v>
       </c>
       <c r="M26" t="n">
-        <v>3.844129919814281</v>
+        <v>3.83369712025317</v>
       </c>
       <c r="N26" t="n">
-        <v>25.74503121437334</v>
+        <v>25.64768729965642</v>
       </c>
       <c r="O26" t="n">
-        <v>5.073956169930259</v>
+        <v>5.064354578784588</v>
       </c>
       <c r="P26" t="n">
-        <v>420.9968972159081</v>
+        <v>420.9879471249437</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -36555,28 +36691,28 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.08665087161825973</v>
+        <v>-0.08778553675465461</v>
       </c>
       <c r="J27" t="n">
+        <v>249</v>
+      </c>
+      <c r="K27" t="n">
         <v>248</v>
       </c>
-      <c r="K27" t="n">
-        <v>247</v>
-      </c>
       <c r="L27" t="n">
-        <v>0.01641252721949182</v>
+        <v>0.01699241383326433</v>
       </c>
       <c r="M27" t="n">
-        <v>4.129935478777516</v>
+        <v>4.118861414313096</v>
       </c>
       <c r="N27" t="n">
-        <v>29.07496272249401</v>
+        <v>28.96640421113512</v>
       </c>
       <c r="O27" t="n">
-        <v>5.392120429153453</v>
+        <v>5.382044612518101</v>
       </c>
       <c r="P27" t="n">
-        <v>418.888888616959</v>
+        <v>418.8992573847229</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -36633,28 +36769,28 @@
         <v>0.07580000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1273353348002634</v>
+        <v>-0.1263772934953052</v>
       </c>
       <c r="J28" t="n">
+        <v>249</v>
+      </c>
+      <c r="K28" t="n">
         <v>248</v>
       </c>
-      <c r="K28" t="n">
-        <v>247</v>
-      </c>
       <c r="L28" t="n">
-        <v>0.03379924893798669</v>
+        <v>0.03361295919489682</v>
       </c>
       <c r="M28" t="n">
-        <v>4.283469098178341</v>
+        <v>4.271443064676311</v>
       </c>
       <c r="N28" t="n">
-        <v>29.9498020178062</v>
+        <v>29.83522418151688</v>
       </c>
       <c r="O28" t="n">
-        <v>5.472641228676168</v>
+        <v>5.462162958161985</v>
       </c>
       <c r="P28" t="n">
-        <v>416.6259381210848</v>
+        <v>416.6171833726742</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -36711,28 +36847,28 @@
         <v>0.1413</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1538198023226858</v>
+        <v>-0.1530250047940101</v>
       </c>
       <c r="J29" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K29" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L29" t="n">
-        <v>0.05707716300420529</v>
+        <v>0.05702496582069638</v>
       </c>
       <c r="M29" t="n">
-        <v>3.841719537007223</v>
+        <v>3.830437899551036</v>
       </c>
       <c r="N29" t="n">
-        <v>25.40628841368365</v>
+        <v>25.30730856871086</v>
       </c>
       <c r="O29" t="n">
-        <v>5.040465098945102</v>
+        <v>5.030636994328935</v>
       </c>
       <c r="P29" t="n">
-        <v>414.5517640681122</v>
+        <v>414.5445098678113</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -36789,28 +36925,28 @@
         <v>0.0956</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1411821077314758</v>
+        <v>-0.1435743247066957</v>
       </c>
       <c r="J30" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K30" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L30" t="n">
-        <v>0.03905496661817576</v>
+        <v>0.04066181491859122</v>
       </c>
       <c r="M30" t="n">
-        <v>4.100615103357337</v>
+        <v>4.095808905118367</v>
       </c>
       <c r="N30" t="n">
-        <v>31.59993056007024</v>
+        <v>31.51143004754919</v>
       </c>
       <c r="O30" t="n">
-        <v>5.621381552614111</v>
+        <v>5.613504257373391</v>
       </c>
       <c r="P30" t="n">
-        <v>416.1348810019111</v>
+        <v>416.1567519679235</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -36867,28 +37003,28 @@
         <v>0.07099999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1606188366860592</v>
+        <v>-0.1627511650885943</v>
       </c>
       <c r="J31" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K31" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L31" t="n">
-        <v>0.04946510272368598</v>
+        <v>0.05113819818367515</v>
       </c>
       <c r="M31" t="n">
-        <v>4.230310682334066</v>
+        <v>4.22266863963987</v>
       </c>
       <c r="N31" t="n">
-        <v>31.94233300701404</v>
+        <v>31.84456570251752</v>
       </c>
       <c r="O31" t="n">
-        <v>5.651754860838714</v>
+        <v>5.643098944951925</v>
       </c>
       <c r="P31" t="n">
-        <v>421.3493494175758</v>
+        <v>421.3688443390242</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -36945,28 +37081,28 @@
         <v>0.0849</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.1444292048931063</v>
+        <v>-0.1453640159140646</v>
       </c>
       <c r="J32" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K32" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L32" t="n">
-        <v>0.04819280376010393</v>
+        <v>0.04922558255170761</v>
       </c>
       <c r="M32" t="n">
-        <v>3.867540607994898</v>
+        <v>3.856862634807044</v>
       </c>
       <c r="N32" t="n">
-        <v>26.54491637843318</v>
+        <v>26.44417511383847</v>
       </c>
       <c r="O32" t="n">
-        <v>5.152175887761712</v>
+        <v>5.142390019615243</v>
       </c>
       <c r="P32" t="n">
-        <v>421.6648916949386</v>
+        <v>421.6734382524955</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -37023,28 +37159,28 @@
         <v>0.0956</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.0651028061313393</v>
+        <v>-0.0670632106024904</v>
       </c>
       <c r="J33" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K33" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L33" t="n">
-        <v>0.009635360924205361</v>
+        <v>0.01030659048617255</v>
       </c>
       <c r="M33" t="n">
-        <v>3.863771050141239</v>
+        <v>3.857038142256172</v>
       </c>
       <c r="N33" t="n">
-        <v>28.06926788080046</v>
+        <v>27.98233271568133</v>
       </c>
       <c r="O33" t="n">
-        <v>5.298043778679114</v>
+        <v>5.289832957256905</v>
       </c>
       <c r="P33" t="n">
-        <v>421.7615719632464</v>
+        <v>421.7794950613613</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -37101,28 +37237,28 @@
         <v>0.0655</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1716711330948949</v>
+        <v>-0.1731486993735327</v>
       </c>
       <c r="J34" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K34" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L34" t="n">
-        <v>0.05032516585064106</v>
+        <v>0.05159892957376189</v>
       </c>
       <c r="M34" t="n">
-        <v>4.357385740291796</v>
+        <v>4.347050208365744</v>
       </c>
       <c r="N34" t="n">
-        <v>35.83346392644672</v>
+        <v>35.70420658332445</v>
       </c>
       <c r="O34" t="n">
-        <v>5.986105906718216</v>
+        <v>5.975299706569073</v>
       </c>
       <c r="P34" t="n">
-        <v>430.2404556822932</v>
+        <v>430.2539644075452</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -37179,28 +37315,28 @@
         <v>0.0956</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1616644127468497</v>
+        <v>-0.164660268861005</v>
       </c>
       <c r="J35" t="n">
+        <v>249</v>
+      </c>
+      <c r="K35" t="n">
         <v>248</v>
       </c>
-      <c r="K35" t="n">
-        <v>247</v>
-      </c>
       <c r="L35" t="n">
-        <v>0.0451216243903646</v>
+        <v>0.04708356344110121</v>
       </c>
       <c r="M35" t="n">
-        <v>4.36313096772701</v>
+        <v>4.358380799857998</v>
       </c>
       <c r="N35" t="n">
-        <v>35.75602587289128</v>
+        <v>35.67237325504062</v>
       </c>
       <c r="O35" t="n">
-        <v>5.979634259124155</v>
+        <v>5.972635369335769</v>
       </c>
       <c r="P35" t="n">
-        <v>434.5452837619641</v>
+        <v>434.5726450626591</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
@@ -37257,28 +37393,28 @@
         <v>0.1394</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2141425912590933</v>
+        <v>-0.2147207626998281</v>
       </c>
       <c r="J36" t="n">
+        <v>249</v>
+      </c>
+      <c r="K36" t="n">
         <v>248</v>
       </c>
-      <c r="K36" t="n">
-        <v>247</v>
-      </c>
       <c r="L36" t="n">
-        <v>0.07514221406738786</v>
+        <v>0.07618599648836966</v>
       </c>
       <c r="M36" t="n">
-        <v>4.803838478178872</v>
+        <v>4.786741665773349</v>
       </c>
       <c r="N36" t="n">
-        <v>36.48834195722341</v>
+        <v>36.34346581382057</v>
       </c>
       <c r="O36" t="n">
-        <v>6.040558083258815</v>
+        <v>6.028554205928696</v>
       </c>
       <c r="P36" t="n">
-        <v>426.4918922177353</v>
+        <v>426.4971726858354</v>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
@@ -37335,28 +37471,28 @@
         <v>0.1224</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.1832093715649088</v>
+        <v>-0.1842237902657339</v>
       </c>
       <c r="J37" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K37" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L37" t="n">
-        <v>0.0415428301154529</v>
+        <v>0.04236729707511822</v>
       </c>
       <c r="M37" t="n">
-        <v>5.102755287498467</v>
+        <v>5.086381809154904</v>
       </c>
       <c r="N37" t="n">
-        <v>49.89724083829176</v>
+        <v>49.70375655693653</v>
       </c>
       <c r="O37" t="n">
-        <v>7.063797904689216</v>
+        <v>7.050089116949978</v>
       </c>
       <c r="P37" t="n">
-        <v>417.0914657730556</v>
+        <v>417.1007401478962</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
@@ -37413,28 +37549,28 @@
         <v>0.1069</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.1085388279823673</v>
+        <v>-0.113983108264197</v>
       </c>
       <c r="J38" t="n">
+        <v>249</v>
+      </c>
+      <c r="K38" t="n">
         <v>248</v>
       </c>
-      <c r="K38" t="n">
-        <v>247</v>
-      </c>
       <c r="L38" t="n">
-        <v>0.01403486623007222</v>
+        <v>0.01554507550725559</v>
       </c>
       <c r="M38" t="n">
-        <v>5.617033486020001</v>
+        <v>5.61506231241597</v>
       </c>
       <c r="N38" t="n">
-        <v>53.47604758937929</v>
+        <v>53.46023300497941</v>
       </c>
       <c r="O38" t="n">
-        <v>7.312731882776729</v>
+        <v>7.311650498005181</v>
       </c>
       <c r="P38" t="n">
-        <v>416.2676758497653</v>
+        <v>416.3174266318009</v>
       </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
@@ -37491,28 +37627,28 @@
         <v>0.2</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1956917921066365</v>
+        <v>-0.1978774127732639</v>
       </c>
       <c r="J39" t="n">
+        <v>249</v>
+      </c>
+      <c r="K39" t="n">
         <v>248</v>
       </c>
-      <c r="K39" t="n">
-        <v>247</v>
-      </c>
       <c r="L39" t="n">
-        <v>0.04069650433393113</v>
+        <v>0.04193423896715243</v>
       </c>
       <c r="M39" t="n">
-        <v>5.889342664401996</v>
+        <v>5.875244434560354</v>
       </c>
       <c r="N39" t="n">
-        <v>58.32837899435066</v>
+        <v>58.12538688800388</v>
       </c>
       <c r="O39" t="n">
-        <v>7.637301813752726</v>
+        <v>7.624000714061082</v>
       </c>
       <c r="P39" t="n">
-        <v>422.6880750910368</v>
+        <v>422.708047673595</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
@@ -37550,7 +37686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN249"/>
+  <dimension ref="A1:AN250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87735,6 +87871,208 @@
         </is>
       </c>
     </row>
+    <row r="250">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>-34.86127501868764,173.29571737239993</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>-34.86144715673825,173.29652353488538</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>-34.86157187810682,173.29734860055635</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>-34.861609743484394,173.29820680723094</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>-34.861599444937916,173.29904310454387</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>-34.86158306169271,173.2999554306285</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>-34.861556360697314,173.30084043261834</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>-34.86153276995809,173.301696477412</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>-34.861444454826305,173.30257430875162</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>-34.861370386521635,173.3034739559844</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>-34.86130256124733,173.30437927832835</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>-34.86124196693241,173.30527049888073</t>
+        </is>
+      </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>-34.86124056130005,173.30616492680846</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>-34.861195682013694,173.3070645964968</t>
+        </is>
+      </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>-34.861157268923115,173.3079808198812</t>
+        </is>
+      </c>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>-34.861195401807365,173.30888224305824</t>
+        </is>
+      </c>
+      <c r="R250" t="inlineStr">
+        <is>
+          <t>-34.861078293644695,173.30975108748933</t>
+        </is>
+      </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>-34.86103376518151,173.31065107107105</t>
+        </is>
+      </c>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>-34.86096636474482,173.31155728107717</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>-34.86086860773862,173.31244772060873</t>
+        </is>
+      </c>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t>-34.86081663944492,173.3133336299306</t>
+        </is>
+      </c>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>-34.86073340228982,173.31420725253435</t>
+        </is>
+      </c>
+      <c r="X250" t="inlineStr">
+        <is>
+          <t>-34.86061727030183,173.31508242856907</t>
+        </is>
+      </c>
+      <c r="Y250" t="inlineStr">
+        <is>
+          <t>-34.86050120215765,173.3159769318853</t>
+        </is>
+      </c>
+      <c r="Z250" t="inlineStr">
+        <is>
+          <t>-34.8604238366867,173.31685926791417</t>
+        </is>
+      </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>-34.86034688204141,173.31774057928627</t>
+        </is>
+      </c>
+      <c r="AB250" t="inlineStr">
+        <is>
+          <t>-34.86023298190693,173.3186328248538</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>-34.860147980928545,173.31954175517464</t>
+        </is>
+      </c>
+      <c r="AD250" t="inlineStr">
+        <is>
+          <t>-34.86009216348871,173.3204510524528</t>
+        </is>
+      </c>
+      <c r="AE250" t="inlineStr">
+        <is>
+          <t>-34.85997545544981,173.32132549558708</t>
+        </is>
+      </c>
+      <c r="AF250" t="inlineStr">
+        <is>
+          <t>-34.85984489991108,173.32219989911275</t>
+        </is>
+      </c>
+      <c r="AG250" t="inlineStr">
+        <is>
+          <t>-34.85973574532361,173.32310405875057</t>
+        </is>
+      </c>
+      <c r="AH250" t="inlineStr">
+        <is>
+          <t>-34.8596072480876,173.32399618975924</t>
+        </is>
+      </c>
+      <c r="AI250" t="inlineStr">
+        <is>
+          <t>-34.85950780185838,173.32481615272604</t>
+        </is>
+      </c>
+      <c r="AJ250" t="inlineStr">
+        <is>
+          <t>-34.859361913700326,173.3256401494801</t>
+        </is>
+      </c>
+      <c r="AK250" t="inlineStr">
+        <is>
+          <t>-34.85922583810369,173.3265650039161</t>
+        </is>
+      </c>
+      <c r="AL250" t="inlineStr">
+        <is>
+          <t>-34.859146468531414,173.3275055914589</t>
+        </is>
+      </c>
+      <c r="AM250" t="inlineStr">
+        <is>
+          <t>-34.85899690397486,173.32840271084467</t>
+        </is>
+      </c>
+      <c r="AN250" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
